--- a/public/downloads/PengTrends2022.xlsx
+++ b/public/downloads/PengTrends2022.xlsx
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9620465416700443</v>
+        <v>-0.9629726596120474</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1716022735464904</v>
+        <v>0.1714993715529345</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1583512762292441</v>
+        <v>0.1582967987032439</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -1709,16 +1709,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.005606554113911832</v>
+        <v>-0.01294417037820583</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7872603749789109</v>
+        <v>0.7875583332431645</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06610540428341119</v>
+        <v>0.06482466581907922</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -1768,16 +1768,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.719118279982356</v>
+        <v>-1.781511278707057</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3886063521907392</v>
+        <v>0.3888147800838755</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1764153478320275</v>
+        <v>0.1610776330172725</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -1827,16 +1827,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.522246944577748</v>
+        <v>-1.413872860037699</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5619631992089003</v>
+        <v>0.5212310873309171</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2534011563733041</v>
+        <v>0.2211242910780791</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -1886,16 +1886,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.85642267087979</v>
+        <v>-1.782911532845173</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5132247111306137</v>
+        <v>0.4898590771395313</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1448988071199989</v>
+        <v>0.1278013611343582</v>
       </c>
       <c r="R7" s="5">
         <v>8</v>
@@ -1945,16 +1945,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.731609676329943</v>
+        <v>-1.693412900035851</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5584596917896314</v>
+        <v>0.5461294829263866</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1065424347838821</v>
+        <v>0.09744554684949325</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -3687,16 +3687,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.473624953563772</v>
+        <v>-1.637522533535957</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.395940020292959</v>
+        <v>0.3777291780738273</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3977749526904177</v>
+        <v>0.3881339185744069</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -3746,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3542390933887418</v>
+        <v>0.1878493146541587</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5075125430937028</v>
+        <v>0.4907714112982325</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3120117072436415</v>
+        <v>0.2723792116319146</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -3919,22 +3919,22 @@
         <v>8</v>
       </c>
       <c r="N7" s="4">
-        <v>-2.925661867883011</v>
+        <v>-3.414413202379365</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.667827636893317</v>
+        <v>0.5299115549302466</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.667827636893317</v>
+        <v>0.3351660324824479</v>
       </c>
       <c r="R7" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -3978,16 +3978,16 @@
         <v>7</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.641769948002548</v>
+        <v>-2.908876817651617</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.6208017372686704</v>
+        <v>0.5633805355876879</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4767556940105351</v>
+        <v>0.3787684834132961</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -5656,22 +5656,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4520968478029251</v>
+        <v>-0.5398975074713817</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2926931510807159</v>
+        <v>0.2781668531360245</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2926931510807159</v>
+        <v>0.1752342253358213</v>
       </c>
       <c r="R3" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -5715,16 +5715,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05153482659857933</v>
+        <v>0.09697201944408462</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1271500755875118</v>
+        <v>0.1192727542519351</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1200573698613325</v>
+        <v>0.1111953833588087</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -5774,16 +5774,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7496472518777928</v>
+        <v>-0.7579457506534624</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1374390695786504</v>
+        <v>0.1357793698235165</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1144577908517929</v>
+        <v>0.1135357354322741</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -5833,16 +5833,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.559987182434307</v>
+        <v>-0.5970535102770818</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1658334783989256</v>
+        <v>0.1505070661412036</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1658334783989256</v>
+        <v>0.1505070661412036</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -5892,16 +5892,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7744723335978774</v>
+        <v>-0.8431349672103305</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2240880251628345</v>
+        <v>0.2081114751678581</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2240880251628345</v>
+        <v>0.2081114751678581</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -5951,16 +5951,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8549154182308631</v>
+        <v>-0.8518930806974225</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.07805330618403455</v>
+        <v>0.07771749090254115</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.07805330618403455</v>
+        <v>0.07771749090254115</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -7729,16 +7729,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7585145498388657</v>
+        <v>-0.8127191193198087</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1758996997971814</v>
+        <v>0.1675258758112048</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1758996997971814</v>
+        <v>0.1675258758112048</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -7788,16 +7788,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1497825256244596</v>
+        <v>0.1601104858164035</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>2.26669056119969</v>
+        <v>2.264778553352395</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09369040120830618</v>
+        <v>0.09283038740409211</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -7847,16 +7847,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.994722913120313</v>
+        <v>-1.027073473942437</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3986834525181621</v>
+        <v>0.4010977899786667</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1645477621852933</v>
+        <v>0.1594780438053931</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -7906,16 +7906,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7124940186376989</v>
+        <v>-0.6952920960466145</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8535901862947463</v>
+        <v>0.8515633969954151</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.08715026432969353</v>
+        <v>0.08702036669183144</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -7965,16 +7965,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.927879573951941</v>
+        <v>-0.9848523571490659</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4517457120875608</v>
+        <v>0.4508052739806266</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.110767901653162</v>
+        <v>0.1025883108832204</v>
       </c>
       <c r="R7" s="5">
         <v>8</v>
@@ -8024,16 +8024,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.085532727238387</v>
+        <v>-1.11435206258102</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>1.385946113783373</v>
+        <v>1.38695984462821</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1105742331214969</v>
+        <v>0.1081122634041094</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -9782,16 +9782,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.916395173974201</v>
+        <v>-0.9459973285265733</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1726736212392917</v>
+        <v>0.1675835462744241</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1726736212392917</v>
+        <v>0.1675835462744241</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -9841,16 +9841,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04519757303617856</v>
+        <v>0.04776773002959089</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6152144573114869</v>
+        <v>0.6148173009324738</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06661152316024527</v>
+        <v>0.06630627930499031</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -9900,16 +9900,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.212061475132032</v>
+        <v>-1.270913872929668</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.802978210897163</v>
+        <v>0.8035622222014354</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1573107814633659</v>
+        <v>0.1433276961442971</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -9959,16 +9959,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2541378944542885</v>
+        <v>-0.8840487889574433</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>1.23781253104759</v>
+        <v>0.7860876014266169</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.7302394271343603</v>
+        <v>0.1494502319073945</v>
       </c>
       <c r="R6" s="5">
         <v>7</v>
@@ -10018,16 +10018,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8172141572099968</v>
+        <v>-1.425261247728486</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>1.200473531130644</v>
+        <v>0.7717850259901348</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.6752663612609872</v>
+        <v>0.1169859066631034</v>
       </c>
       <c r="R7" s="5">
         <v>8</v>
@@ -10077,13 +10077,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.209254803654403</v>
+        <v>-1.225890949604945</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.6892651023883647</v>
+        <v>0.6911135630495361</v>
       </c>
       <c r="Q8" s="4">
         <v>0.1077840331454354</v>
@@ -11843,16 +11843,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.005174358527559</v>
+        <v>-1.002913872376666</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1157560262909774</v>
+        <v>0.1155926519865413</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1157560262909774</v>
+        <v>0.1155926519865413</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -11902,16 +11902,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.174214495096976</v>
+        <v>-0.1841273373829608</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7467178312381293</v>
+        <v>0.7471257995039196</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08521303194399366</v>
+        <v>0.08443289095725959</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -11961,7 +11961,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="4">
-        <v>-2.014789706901259</v>
+        <v>-2.036377853350132</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
@@ -11970,7 +11970,7 @@
         <v>0.3263576436664152</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1514373373739309</v>
+        <v>0.1490386544351673</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -12020,16 +12020,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.595165851676029</v>
+        <v>-1.43656307996207</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.6343418160024359</v>
+        <v>0.5709261288474308</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2560799351226706</v>
+        <v>0.2045626335375346</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -12079,16 +12079,16 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>-2.013448955665808</v>
+        <v>-1.973304380520858</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4811432554650107</v>
+        <v>0.4682304011621454</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1003727354946022</v>
+        <v>0.09086384629699751</v>
       </c>
       <c r="R7" s="5">
         <v>8</v>
@@ -12136,16 +12136,16 @@
         <v>8</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.184327664372177</v>
+        <v>-2.164078125140804</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.281901202638134</v>
+        <v>0.2781172368761165</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.08721422264761713</v>
+        <v>0.08548845356926904</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -13850,7 +13850,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2787323025438766</v>
+        <v>-0.2872682602573926</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
@@ -13909,16 +13909,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1648853093020659</v>
+        <v>0.1622895581531343</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05188626880661126</v>
+        <v>0.05159785201228553</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03779034646306557</v>
+        <v>0.03763765521901077</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -13968,16 +13968,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.08726199292214165</v>
+        <v>-0.1168895684095066</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05489425859471666</v>
+        <v>0.04905748963865886</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05489425859471666</v>
+        <v>0.04905748963865886</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -14027,13 +14027,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.08588464761124803</v>
+        <v>-0.0776058964183779</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.04068853563834356</v>
+        <v>0.0416083968819958</v>
       </c>
       <c r="Q6" s="4">
         <v>0.04509868232706338</v>
@@ -14086,16 +14086,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2029651297723666</v>
+        <v>-0.2163757011585279</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.05726653191096689</v>
+        <v>0.0546319074564939</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.05726653191096689</v>
+        <v>0.0546319074564939</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -14145,16 +14145,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.06423458699848676</v>
+        <v>-0.07832626328310432</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.04387829073002041</v>
+        <v>0.04095537723090557</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.04387829073002041</v>
+        <v>0.04095537723090557</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -15911,16 +15911,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.620430021905935</v>
+        <v>-0.6616089750859828</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1094393547257119</v>
+        <v>0.1061217170861403</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1094393547257119</v>
+        <v>0.1061217170861403</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -15970,16 +15970,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3678306625534877</v>
+        <v>-0.3556795953773317</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1110593585142796</v>
+        <v>0.1105795841372574</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0739382929677103</v>
+        <v>0.07271552791108939</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -16029,16 +16029,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.092698962197268</v>
+        <v>-1.146115875439136</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1764478143976476</v>
+        <v>0.1681579771197058</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1575029069823057</v>
+        <v>0.1423567640910516</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -16088,13 +16088,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.9592731820230154</v>
+        <v>-0.9800547325757876</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1107887507516546</v>
+        <v>0.1084796895791244</v>
       </c>
       <c r="Q6" s="4">
         <v>0.1216471182324352</v>
@@ -16147,16 +16147,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.368968755218699</v>
+        <v>-1.415254692208707</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1609312531730629</v>
+        <v>0.1397625362114936</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1626426368116096</v>
+        <v>0.1446135723535953</v>
       </c>
       <c r="R7" s="5">
         <v>8</v>
@@ -16206,16 +16206,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.080271660453942</v>
+        <v>-1.130741992139493</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1430694313597215</v>
+        <v>0.1295314815162948</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1312540772155207</v>
+        <v>0.1223326751023595</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -17972,16 +17972,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3261326442235338</v>
+        <v>-0.310889907799706</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09024938809298168</v>
+        <v>0.08891115651830524</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09024938809298168</v>
+        <v>0.08891115651830524</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -18031,7 +18031,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.197434747533195</v>
+        <v>0.2024720050540201</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
@@ -18040,7 +18040,7 @@
         <v>0.05441690589920394</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04003399363971836</v>
+        <v>0.03973768437378748</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -18090,16 +18090,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1506238577211592</v>
+        <v>-0.1603690792689907</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04118545576694558</v>
+        <v>0.03932871771320219</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04357547531954398</v>
+        <v>0.04042963064340337</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -18149,16 +18149,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1390945947100116</v>
+        <v>-0.1480654487895539</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.04279446648791971</v>
+        <v>0.04179770492352613</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.04279446648791971</v>
+        <v>0.04179770492352613</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -18208,16 +18208,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2495550109540741</v>
+        <v>-0.2526429273566482</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.0582967849504329</v>
+        <v>0.05750617199049578</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.0582967849504329</v>
+        <v>0.05750617199049578</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -18267,16 +18267,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1251214435809228</v>
+        <v>-0.1229939205877599</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.04186408201725867</v>
+        <v>0.04162769057357391</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.04186408201725867</v>
+        <v>0.04162769057357391</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -20033,16 +20033,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.516054494355155</v>
+        <v>-0.4951934355594929</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1490535304582829</v>
+        <v>0.1490012006921015</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1490535304582829</v>
+        <v>0.1490012006921015</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -20092,7 +20092,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1903142769335719</v>
+        <v>-0.1954599196251436</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
@@ -20151,16 +20151,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4701187468623679</v>
+        <v>-0.5147741384643609</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1714506879228178</v>
+        <v>0.1574044885586829</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1805050725767274</v>
+        <v>0.1698598945723546</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -20210,16 +20210,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6863291991685334</v>
+        <v>-0.7134599426535502</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1516282847167379</v>
+        <v>0.147864576041498</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1613421947859063</v>
+        <v>0.1604993654618885</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -20269,16 +20269,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8398617632119504</v>
+        <v>-0.905833709810338</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1998187545864599</v>
+        <v>0.1723284957252847</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1998187545864599</v>
+        <v>0.1723284957252847</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -20328,16 +20328,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4035934707249328</v>
+        <v>-0.3579510234339409</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1496577080725452</v>
+        <v>0.1445863250402127</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.08214926139726651</v>
+        <v>0.07562891178426767</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -22058,13 +22058,13 @@
         <v>19.8019801980198</v>
       </c>
       <c r="H3" s="4">
-        <v>1.387356859852948</v>
+        <v>1.378511963800133</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2656613593873814</v>
+        <v>0.2521421517068456</v>
       </c>
       <c r="J3" s="4">
-        <v>3.078782255199414</v>
+        <v>3.07765095764694</v>
       </c>
       <c r="K3" s="4">
         <v>81.99501582811367</v>
@@ -22108,13 +22108,13 @@
         <v>16.83168316831683</v>
       </c>
       <c r="H4" s="4">
-        <v>0.8305414692553402</v>
+        <v>0.8271139979899251</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2660288151385932</v>
+        <v>0.2582957742640954</v>
       </c>
       <c r="J4" s="4">
-        <v>0.8093889967252372</v>
+        <v>0.8130881613839603</v>
       </c>
       <c r="K4" s="4">
         <v>72.43955007745683</v>
@@ -22158,13 +22158,13 @@
         <v>1.98019801980198</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5937764148288175</v>
+        <v>0.5762532086513296</v>
       </c>
       <c r="I5" s="4">
-        <v>0.5561035962935211</v>
+        <v>0.5353861290809026</v>
       </c>
       <c r="J5" s="4">
-        <v>0.6406840659198072</v>
+        <v>0.6166474993980667</v>
       </c>
       <c r="K5" s="4">
         <v>81.23122516333265</v>
@@ -22208,13 +22208,13 @@
         <v>7.920792079207921</v>
       </c>
       <c r="H6" s="4">
-        <v>0.6480210070114961</v>
+        <v>0.6469647625327516</v>
       </c>
       <c r="I6" s="4">
-        <v>0.4548058247479677</v>
+        <v>0.4479636029459874</v>
       </c>
       <c r="J6" s="4">
-        <v>0.7326556423883605</v>
+        <v>0.7324449397208738</v>
       </c>
       <c r="K6" s="4">
         <v>82.2906984576009</v>
@@ -22258,13 +22258,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.573276213622684</v>
+        <v>0.5707798370791298</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3664070600257091</v>
+        <v>0.3629798731709207</v>
       </c>
       <c r="J7" s="4">
-        <v>0.9979714050030704</v>
+        <v>0.9943314029552843</v>
       </c>
       <c r="K7" s="4">
         <v>84.61945174109283</v>
@@ -22308,13 +22308,13 @@
         <v>5.940594059405941</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8161494989325534</v>
+        <v>0.8093944860534755</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4494747015268698</v>
+        <v>0.4419679480673835</v>
       </c>
       <c r="J8" s="4">
-        <v>1.265715378109716</v>
+        <v>1.260436702673436</v>
       </c>
       <c r="K8" s="4">
         <v>79.25742574257433</v>
@@ -22340,13 +22340,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>55.44554455445545</v>
+        <v>54.45544554455446</v>
       </c>
       <c r="C9" s="3">
         <v>18.81188118811881</v>
       </c>
       <c r="D9" s="3">
-        <v>25.74257425742574</v>
+        <v>26.73267326732674</v>
       </c>
       <c r="E9" s="3">
         <v>0.9900990099009901</v>
@@ -22355,16 +22355,16 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>24.75247524752475</v>
+        <v>25.74257425742574</v>
       </c>
       <c r="H9" s="4">
-        <v>1.582941412107295</v>
+        <v>1.55930605482948</v>
       </c>
       <c r="I9" s="4">
-        <v>0.515514358088095</v>
+        <v>0.4355957888402786</v>
       </c>
       <c r="J9" s="4">
-        <v>1.498204015814419</v>
+        <v>1.486479964246022</v>
       </c>
       <c r="K9" s="4">
         <v>77.39812756785896</v>
@@ -22390,13 +22390,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>97.02970297029702</v>
+        <v>96.03960396039604</v>
       </c>
       <c r="C10" s="3">
         <v>2.97029702970297</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -22405,16 +22405,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3496162143986273</v>
+        <v>0.3426398664540344</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3530528942178275</v>
+        <v>0.3286066955049423</v>
       </c>
       <c r="J10" s="4">
-        <v>0.354547860845018</v>
+        <v>0.3472858156743325</v>
       </c>
       <c r="K10" s="4">
         <v>84.35172088637471</v>
@@ -22458,13 +22458,13 @@
         <v>1.98019801980198</v>
       </c>
       <c r="H11" s="4">
-        <v>1.054122323426706</v>
+        <v>1.052354174244065</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3911571085020242</v>
+        <v>0.3878849909216227</v>
       </c>
       <c r="J11" s="4">
-        <v>2.52476198079709</v>
+        <v>2.522455287096602</v>
       </c>
       <c r="K11" s="4">
         <v>75.54320738196236</v>
@@ -22508,13 +22508,13 @@
         <v>1.98019801980198</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8630134158447814</v>
+        <v>0.7838053483393367</v>
       </c>
       <c r="I12" s="4">
-        <v>0.5400248327504729</v>
+        <v>0.4418244654120367</v>
       </c>
       <c r="J12" s="4">
-        <v>1.135542391784257</v>
+        <v>1.052175944279358</v>
       </c>
       <c r="K12" s="4">
         <v>79.07085606519843</v>
@@ -22558,13 +22558,13 @@
         <v>13.86138613861386</v>
       </c>
       <c r="H13" s="4">
-        <v>0.8455023255504599</v>
+        <v>0.8384071782863547</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3099722286594235</v>
+        <v>0.303149104373282</v>
       </c>
       <c r="J13" s="4">
-        <v>1.960820763971862</v>
+        <v>1.95649707267105</v>
       </c>
       <c r="K13" s="4">
         <v>82.58772816057166</v>
@@ -22608,13 +22608,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1043974257778921</v>
+        <v>0.1033548685279133</v>
       </c>
       <c r="I14" s="4">
-        <v>0.09117243368436317</v>
+        <v>0.09001637866049027</v>
       </c>
       <c r="J14" s="4">
-        <v>0.09450952447504866</v>
+        <v>0.09140368145917999</v>
       </c>
       <c r="K14" s="4">
         <v>96.43497002761622</v>
@@ -22658,13 +22658,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.4351727244782017</v>
+        <v>0.4303767508061637</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3979734781485535</v>
+        <v>0.3933237630725799</v>
       </c>
       <c r="J15" s="4">
-        <v>0.4383129301443086</v>
+        <v>0.4299310558885887</v>
       </c>
       <c r="K15" s="4">
         <v>78.44615073752288</v>
@@ -22708,13 +22708,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1187579930013359</v>
+        <v>0.1181553252528829</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1052432689685052</v>
+        <v>0.1044552281178552</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1108316234350455</v>
+        <v>0.1109328561990885</v>
       </c>
       <c r="K16" s="4">
         <v>96.40836532632893</v>
@@ -22758,13 +22758,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2826107645972151</v>
+        <v>0.2779738132650236</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2441913925772926</v>
+        <v>0.2398811105178977</v>
       </c>
       <c r="J17" s="4">
-        <v>0.4275062847820338</v>
+        <v>0.4241007694460172</v>
       </c>
       <c r="K17" s="4">
         <v>80.02795177476948</v>
@@ -23911,22 +23911,22 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5">
         <v>19</v>
       </c>
       <c r="D9" s="5">
+        <v>27</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
         <v>26</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>25</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>
@@ -23955,13 +23955,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="5">
         <v>3</v>
       </c>
       <c r="D10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="5">
         <v>0</v>
@@ -23970,7 +23970,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
@@ -24461,7 +24461,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.487088719845512</v>
+        <v>-1.474149047357059</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
@@ -24520,16 +24520,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1406756511585172</v>
+        <v>0.115871663314465</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>2.716488712900779</v>
+        <v>2.716727971832774</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.127524312682425</v>
+        <v>0.1246929805004129</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -24579,16 +24579,16 @@
         <v>8</v>
       </c>
       <c r="N5" s="4">
-        <v>-2.580874038837566</v>
+        <v>-2.73875396404037</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4544646263118516</v>
+        <v>0.4109560965611309</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.28771258959957</v>
+        <v>0.2218275648540132</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -24638,16 +24638,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.069728735053104</v>
+        <v>-1.945977783208946</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.6104306577586208</v>
+        <v>0.5616829882953122</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2635290852081198</v>
+        <v>0.2241568260424174</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -24695,13 +24695,13 @@
         <v>8</v>
       </c>
       <c r="N7" s="4">
-        <v>-2.575128795753699</v>
+        <v>-2.55948359906688</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5042073025373005</v>
+        <v>0.5024689473498761</v>
       </c>
       <c r="Q7" s="4">
         <v>0.09807171678039595</v>
@@ -24752,16 +24752,16 @@
         <v>8</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.696419301029891</v>
+        <v>-2.721895208014757</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3249136837522302</v>
+        <v>0.3240046123359611</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1298558264238636</v>
+        <v>0.1256486327074526</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -26442,16 +26442,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.468144494745074</v>
+        <v>-1.495174552030221</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2134714891850379</v>
+        <v>0.2115235108348214</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2198719260500137</v>
+        <v>0.2162193573683052</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -26501,16 +26501,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4065958767263914</v>
+        <v>0.3459285193530377</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1505688655400903</v>
+        <v>0.1416375924784208</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1505688655400903</v>
+        <v>0.1416375924784208</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -26558,16 +26558,16 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>-2.632318325379206</v>
+        <v>-2.727390343679872</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3054258972457319</v>
+        <v>0.3058178030252748</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3408166092534773</v>
+        <v>0.3272348923533822</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -26617,16 +26617,16 @@
         <v>7</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.241996768080753</v>
+        <v>-2.169026231771568</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2254298851596306</v>
+        <v>0.2216363289941607</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1966639071047211</v>
+        <v>0.1832748393799193</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -26674,16 +26674,16 @@
         <v>9</v>
       </c>
       <c r="N7" s="4">
-        <v>-2.679170011837818</v>
+        <v>-2.749863569661102</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1712496275061391</v>
+        <v>0.1586999403079972</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1712496275061391</v>
+        <v>0.1586999403079972</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -26731,16 +26731,16 @@
         <v>8</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.279922166683718</v>
+        <v>-2.268309491217224</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.07992634589401051</v>
+        <v>0.07912879701446703</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.07550789518995771</v>
+        <v>0.07315906826715945</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -28417,16 +28417,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7466808506257318</v>
+        <v>-0.8083083909587003</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1692722997606863</v>
+        <v>0.1652292333518643</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1692722997606863</v>
+        <v>0.1652292333518643</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -28476,16 +28476,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.045490317097788</v>
+        <v>-0.05713590195955476</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3077363240723583</v>
+        <v>0.2604129457401238</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1865687224002854</v>
+        <v>0.1333299217765216</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -28535,16 +28535,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.258061496897426</v>
+        <v>-1.414867822859378</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3344755737452942</v>
+        <v>0.3095865011266142</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2958908873219376</v>
+        <v>0.2379341655864014</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -28594,16 +28594,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.191790617221159</v>
+        <v>-1.205673854259658</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1576548108281107</v>
+        <v>0.1569521896688255</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.08264896172454428</v>
+        <v>0.08012310829053604</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -28653,16 +28653,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.460253693354995</v>
+        <v>-1.560316104267258</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3158832609721382</v>
+        <v>0.3017045743706856</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3158832609721382</v>
+        <v>0.3017045743706856</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -28712,16 +28712,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.190170060015589</v>
+        <v>-1.348633936344413</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2901591367851021</v>
+        <v>0.2387785453902325</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3143671364023248</v>
+        <v>0.2608797715038236</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -30482,13 +30482,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9279710955690916</v>
+        <v>-0.9228550923362491</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1373529357835095</v>
+        <v>0.1367844909798603</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1396783978782423</v>
@@ -30541,16 +30541,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0496930066285131</v>
+        <v>-0.0007518002821598202</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2723907950013704</v>
+        <v>0.267706299373458</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1042484889505431</v>
+        <v>0.09526410706966999</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -30600,16 +30600,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.81207601959007</v>
+        <v>-1.83104242610716</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3893055106872149</v>
+        <v>0.3948640811147925</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1139607933712089</v>
+        <v>0.1105808064057783</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -30659,16 +30659,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.142146132525037</v>
+        <v>-1.069036999539094</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.270642639936004</v>
+        <v>0.2785483264827538</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1455729309980396</v>
+        <v>0.1208768943251926</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -30718,16 +30718,16 @@
         <v>4</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.886406937598723</v>
+        <v>-1.937391226216278</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1854964604678156</v>
+        <v>0.1798315395103095</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1854964604678156</v>
+        <v>0.1798315395103095</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -30777,16 +30777,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.54869610309288</v>
+        <v>-1.647145107624965</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2626194191582019</v>
+        <v>0.2528549348066412</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1920145973285798</v>
+        <v>0.1687234268665634</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -32519,7 +32519,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7353883980122191</v>
+        <v>-0.7393043281008431</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
@@ -32578,16 +32578,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04802914315613244</v>
+        <v>0.0362520771122945</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6701461703497833</v>
+        <v>0.6698258634442027</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05285926572342965</v>
+        <v>0.05165621279983108</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -32637,7 +32637,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.9468910625598963</v>
+        <v>-1.019113552923955</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
@@ -32646,7 +32646,7 @@
         <v>1.08412075648157</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1374428053950621</v>
+        <v>0.1294180842435</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -32696,16 +32696,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7367845279570449</v>
+        <v>-0.7467849576496519</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1736589836498886</v>
+        <v>0.1719265401584885</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1736589836498886</v>
+        <v>0.1719265401584885</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -32755,16 +32755,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.078892429033456</v>
+        <v>-1.123886761852191</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.184679530622771</v>
+        <v>0.1625720311882712</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.184679530622771</v>
+        <v>0.1625720311882712</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -32814,16 +32814,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.034314455982894</v>
+        <v>-1.021036282440036</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1918248114361631</v>
+        <v>0.1882904758511156</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.06761690354187522</v>
+        <v>0.06530054770155402</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
